--- a/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/ValueSet-AtSchedulingServiceType.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Property</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T10:12:02+00:00</t>
+    <t>2025-01-28T14:00:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>ToDo</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -301,26 +304,28 @@
       <c r="A11" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" t="s" s="2">
+        <v>19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
